--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260901.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>10,800,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.22%</t>
+          <t>15.86%</t>
         </is>
       </c>
     </row>
@@ -638,117 +638,117 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>6.47%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>2,110,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.48%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>8,460,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.43%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2,110,000</t>
+          <t>8,460,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>4.95%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>1,115,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>3.99%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>1,115,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.95%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.70%</t>
         </is>
       </c>
     </row>
@@ -792,29 +792,29 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.58%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>9,785,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
@@ -836,95 +836,95 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>650,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>650,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -990,222 +990,222 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,900,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>1,900,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,050,000</t>
+          <t>149,500</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>149,500</t>
+          <t>1,050,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>1,737,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,737,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>5,360,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>5,360,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,22 +1217,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1276,29 +1276,29 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>860,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1327,220 +1327,220 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>3,100,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>12,457,357,495</t>
+          <t>8,461,882,340</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>2,162,354,124</t>
+          <t>2,668,305,718</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>3,300,089,384</t>
+          <t>4,176,089,384</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
